--- a/sample_data/receiving_materials/Receiving_SAMPLE_m0.xlsx
+++ b/sample_data/receiving_materials/Receiving_SAMPLE_m0.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>501043092</t>
+          <t>509315137</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -510,19 +510,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>104</v>
+        <v>1619</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -531,22 +531,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INV-0030</t>
+          <t>INV-0033</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>457106512</t>
+          <t>456347476</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -558,27 +558,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>504002466</t>
+          <t>507849452</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46299</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>469</v>
+        <v>386</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -587,22 +587,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INV-0020</t>
+          <t>INV-0048</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>455165165</t>
+          <t>458944327</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -614,27 +614,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>505550953</t>
+          <t>506045519</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>254</v>
+        <v>1161</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,22 +643,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INV-0032</t>
+          <t>INV-0026</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>451883692</t>
+          <t>457987842</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -670,27 +670,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>509653253</t>
+          <t>503249703</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46306</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SMP-RM-0003</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1806</v>
+        <v>426</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -699,22 +699,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INV-0029</t>
+          <t>INV-0021</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>455736323</t>
+          <t>452326581</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>506491198</t>
+          <t>507225647</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -738,15 +738,15 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0007</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -755,22 +755,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INV-0023</t>
+          <t>INV-0017</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>454366703</t>
+          <t>457327828</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -782,27 +782,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>506098752</t>
+          <t>501663497</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46302</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0019</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1221</v>
+        <v>1493</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -811,12 +811,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INV-0031</t>
+          <t>INV-0042</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>454278644</t>
+          <t>454640933</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -838,11 +838,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>505112546</t>
+          <t>506586214</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -850,15 +850,15 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0007</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>1929</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INV-0014</t>
+          <t>INV-0012</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>456812025</t>
+          <t>452968239</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -894,27 +894,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>506620658</t>
+          <t>505070038</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SMP-RM-0013</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1748</v>
+        <v>1140</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -923,22 +923,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INV-0047</t>
+          <t>INV-0020</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>456159172</t>
+          <t>455748945</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -950,11 +950,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>509888812</t>
+          <t>509953163</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>46308</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SMP-RM-0016</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1978</v>
+        <v>746</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -979,22 +979,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INV-0003</t>
+          <t>INV-0032</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>453388630</t>
+          <t>459342928</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -1006,11 +1006,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>502560728</t>
+          <t>508876742</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1018,15 +1018,15 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0012</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>855</v>
+        <v>650</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1035,22 +1035,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INV-0044</t>
+          <t>INV-0026</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>457249378</t>
+          <t>451766977</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1062,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>502603516</t>
+          <t>503448176</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SMP-RM-0013</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>163</v>
+        <v>1924</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>452044933</t>
+          <t>458005797</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>504972370</t>
+          <t>504291551</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1906</v>
+        <v>1176</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INV-0051</t>
+          <t>INV-0053</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>457592651</t>
+          <t>455122665</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1174,11 +1174,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>506336123</t>
+          <t>506663388</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1186,15 +1186,15 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>162</v>
+        <v>953</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INV-0012</t>
+          <t>INV-0010</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>453283577</t>
+          <t>456908535</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>502828260</t>
+          <t>509192588</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1238,19 +1238,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46287</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>930</v>
+        <v>1083</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1259,22 +1259,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>INV-0029</t>
+          <t>INV-0002</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>456268604</t>
+          <t>452247057</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>509991321</t>
+          <t>501107102</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1298,15 +1298,15 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46298</v>
+        <v>46285</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>641</v>
+        <v>149</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INV-0029</t>
+          <t>INV-0045</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>455446095</t>
+          <t>453533857</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1342,27 +1342,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>502517010</t>
+          <t>509484790</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>46284</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SMP-RM-0010</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1702</v>
+        <v>1275</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1371,22 +1371,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>INV-0045</t>
+          <t>INV-0040</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>451676621</t>
+          <t>459106820</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1398,11 +1398,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>503488460</t>
+          <t>501263935</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1410,15 +1410,15 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46305</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1993</v>
+        <v>852</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1427,22 +1427,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INV-0022</t>
+          <t>INV-0000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>457647878</t>
+          <t>451280618</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>506013715</t>
+          <t>509988193</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SMP-RM-0001</t>
+          <t>SMP-RM-0017</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1959</v>
+        <v>1675</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1483,22 +1483,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INV-0025</t>
+          <t>INV-0044</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>458586676</t>
+          <t>458223819</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>505191831</t>
+          <t>502795437</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1518,19 +1518,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SMP-RM-0004</t>
+          <t>SMP-RM-0005</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1656</v>
+        <v>503</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1539,22 +1539,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INV-0050</t>
+          <t>INV-0012</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>453345338</t>
+          <t>459832465</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1566,11 +1566,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>502034637</t>
+          <t>505484964</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1578,15 +1578,15 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46308</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SMP-RM-0007</t>
+          <t>SMP-RM-0012</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1696</v>
+        <v>1974</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1600,17 +1600,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>457245146</t>
+          <t>458700704</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>505342289</t>
+          <t>504789255</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>414</v>
+        <v>1348</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1651,22 +1651,22 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INV-0057</t>
+          <t>INV-0054</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>458439543</t>
+          <t>451531577</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1678,27 +1678,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>502543145</t>
+          <t>507362994</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>46286</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1939</v>
+        <v>124</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1707,22 +1707,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INV-0029</t>
+          <t>INV-0040</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>451849559</t>
+          <t>451158547</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -1734,11 +1734,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>508267158</t>
+          <t>502387242</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1746,15 +1746,15 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>46306</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SMP-RM-0001</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>793</v>
+        <v>1168</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1763,22 +1763,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INV-0043</t>
+          <t>INV-0054</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>458158234</t>
+          <t>452599906</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1790,27 +1790,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>504602338</t>
+          <t>501713900</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>46306</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0019</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>923</v>
+        <v>983</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1819,22 +1819,22 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INV-0056</t>
+          <t>INV-0017</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>453493621</t>
+          <t>451781180</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -1846,27 +1846,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>505123584</t>
+          <t>505703878</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>46310</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1817</v>
+        <v>377</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1875,22 +1875,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INV-0035</t>
+          <t>INV-0059</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>459036805</t>
+          <t>456276177</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>505693862</t>
+          <t>503419132</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1914,15 +1914,15 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>418</v>
+        <v>342</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1931,22 +1931,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INV-0041</t>
+          <t>INV-0036</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>459821696</t>
+          <t>455034453</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>501327658</t>
+          <t>506565503</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1970,15 +1970,15 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>46304</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0005</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>992</v>
+        <v>1628</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1987,22 +1987,22 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>INV-0034</t>
+          <t>INV-0044</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>459131572</t>
+          <t>452315798</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -2014,11 +2014,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>509428760</t>
+          <t>501900876</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2026,15 +2026,15 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>378</v>
+        <v>1727</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2043,22 +2043,22 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INV-0001</t>
+          <t>INV-0004</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>456349877</t>
+          <t>456714198</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -2070,11 +2070,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>501491630</t>
+          <t>507655572</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SMP-RM-0016</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1094</v>
+        <v>1614</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2099,22 +2099,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>INV-0022</t>
+          <t>INV-0028</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>454905100</t>
+          <t>459230960</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -2126,27 +2126,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>505158351</t>
+          <t>507298619</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SMP-RM-0018</t>
+          <t>SMP-RM-0019</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1681</v>
+        <v>1363</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2155,22 +2155,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INV-0050</t>
+          <t>INV-0024</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>451937991</t>
+          <t>452437708</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>507516648</t>
+          <t>505955645</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
@@ -2198,11 +2198,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>494</v>
+        <v>178</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2211,22 +2211,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INV-0037</t>
+          <t>INV-0017</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>456335227</t>
+          <t>453587398</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>501473227</t>
+          <t>507536772</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46286</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2267,22 +2267,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INV-0036</t>
+          <t>INV-0000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>454158036</t>
+          <t>456171869</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -2294,27 +2294,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>506185050</t>
+          <t>505525929</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>46285</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>194</v>
+        <v>393</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INV-0003</t>
+          <t>INV-0027</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>454902772</t>
+          <t>458530347</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -2350,19 +2350,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>501334336</t>
+          <t>509597330</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>689</v>
+        <v>193</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2379,22 +2379,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INV-0058</t>
+          <t>INV-0022</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>454380011</t>
+          <t>452561359</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2406,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>506716988</t>
+          <t>506443037</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46286</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>54</v>
+        <v>857</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2435,22 +2435,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INV-0009</t>
+          <t>INV-0024</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>453376537</t>
+          <t>452421022</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -2462,11 +2462,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>509829762</t>
+          <t>505072543</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2474,15 +2474,15 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1452</v>
+        <v>357</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2491,22 +2491,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INV-0042</t>
+          <t>INV-0008</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>457636992</t>
+          <t>455511711</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -2518,27 +2518,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>506646557</t>
+          <t>509273246</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SMP-RM-0005</t>
+          <t>SMP-RM-0006</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>332</v>
+        <v>900</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2547,22 +2547,22 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>INV-0046</t>
+          <t>INV-0017</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>458329435</t>
+          <t>458064924</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -2574,27 +2574,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>506323132</t>
+          <t>502290526</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>46286</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SMP-RM-0018</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1430</v>
+        <v>1486</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INV-0056</t>
+          <t>INV-0040</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>456986539</t>
+          <t>459318184</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>503941912</t>
+          <t>504280754</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>46304</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SMP-RM-0010</t>
+          <t>SMP-RM-0005</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>270</v>
+        <v>633</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>INV-0011</t>
+          <t>INV-0000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>451030163</t>
+          <t>457638609</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2686,27 +2686,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>507569981</t>
+          <t>507373495</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46289</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SMP-RM-0020</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>661</v>
+        <v>891</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>INV-0058</t>
+          <t>INV-0052</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>454706007</t>
+          <t>453283789</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>502746679</t>
+          <t>504369728</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2750,19 +2750,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>46291</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0006</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1536</v>
+        <v>1985</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2771,22 +2771,22 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INV-0004</t>
+          <t>INV-0025</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>454992909</t>
+          <t>456354241</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -2798,27 +2798,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>503816683</t>
+          <t>505067204</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>924</v>
+        <v>1682</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2827,22 +2827,22 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INV-0000</t>
+          <t>INV-0050</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>455449526</t>
+          <t>457592357</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -2854,27 +2854,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>502137407</t>
+          <t>504352088</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SMP-RM-0004</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1485</v>
+        <v>65</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2883,22 +2883,22 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INV-0000</t>
+          <t>INV-0046</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>451807780</t>
+          <t>458744735</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -2910,27 +2910,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>508040612</t>
+          <t>508356053</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>46299</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SMP-RM-0016</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1815</v>
+        <v>1687</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2939,22 +2939,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>INV-0024</t>
+          <t>INV-0054</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>456892681</t>
+          <t>457864256</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -2966,27 +2966,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>502701688</t>
+          <t>503335038</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>343</v>
+        <v>1358</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INV-0028</t>
+          <t>INV-0009</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>452236638</t>
+          <t>458098909</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3022,15 +3022,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>505947745</t>
+          <t>502240929</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
@@ -3038,11 +3038,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1959</v>
+        <v>1202</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3051,22 +3051,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INV-0006</t>
+          <t>INV-0025</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>452244876</t>
+          <t>459965197</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -3078,11 +3078,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>507299138</t>
+          <t>501616817</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3090,15 +3090,15 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>46301</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SMP-RM-0003</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1130</v>
+        <v>1226</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3107,22 +3107,22 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>INV-0057</t>
+          <t>INV-0040</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>452562037</t>
+          <t>452425760</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -3134,27 +3134,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>509098979</t>
+          <t>506956059</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0020</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1253</v>
+        <v>100</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>INV-0056</t>
+          <t>INV-0036</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>458284673</t>
+          <t>457704473</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -3190,11 +3190,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>502698824</t>
+          <t>508221845</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3202,15 +3202,15 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46306</v>
+        <v>46287</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SMP-RM-0007</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>848</v>
+        <v>539</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3219,22 +3219,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>INV-0044</t>
+          <t>INV-0014</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>455450404</t>
+          <t>459567725</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -3246,27 +3246,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>505989554</t>
+          <t>504708297</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>814</v>
+        <v>958</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3275,22 +3275,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>INV-0036</t>
+          <t>INV-0049</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>459236745</t>
+          <t>459396422</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>507053704</t>
+          <t>501412092</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SMP-RM-0003</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>613</v>
+        <v>861</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3331,22 +3331,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>INV-0052</t>
+          <t>INV-0058</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>459058573</t>
+          <t>452440404</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -3358,27 +3358,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>501431773</t>
+          <t>506843985</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>46305</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SMP-RM-0010</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>177</v>
+        <v>1616</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3387,22 +3387,22 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>INV-0030</t>
+          <t>INV-0013</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>452937918</t>
+          <t>459742856</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -3414,27 +3414,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>508901136</t>
+          <t>508988681</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>196</v>
+        <v>663</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3443,22 +3443,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>INV-0041</t>
+          <t>INV-0004</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>457501626</t>
+          <t>456037595</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>507399588</t>
+          <t>501378915</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3478,19 +3478,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>101</v>
+        <v>1396</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3499,22 +3499,22 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>INV-0016</t>
+          <t>INV-0051</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>458377620</t>
+          <t>453757404</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -3526,11 +3526,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>504795715</t>
+          <t>509656941</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3538,15 +3538,15 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>46297</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0006</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>319</v>
+        <v>687</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3555,22 +3555,22 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>INV-0048</t>
+          <t>INV-0035</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>452622400</t>
+          <t>458153291</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -3582,27 +3582,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>507945543</t>
+          <t>507795568</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46309</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0014</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1731</v>
+        <v>820</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3611,22 +3611,22 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>INV-0024</t>
+          <t>INV-0001</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>459767475</t>
+          <t>454310554</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -3638,27 +3638,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>508966231</t>
+          <t>508206700</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SMP-RM-0010</t>
+          <t>SMP-RM-0007</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>171</v>
+        <v>431</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>INV-0025</t>
+          <t>INV-0017</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>451582647</t>
+          <t>452049645</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3694,27 +3694,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>509670757</t>
+          <t>504136665</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0007</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>364</v>
+        <v>947</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3723,22 +3723,22 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>INV-0010</t>
+          <t>INV-0007</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>454554926</t>
+          <t>455401559</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -3750,27 +3750,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>503117049</t>
+          <t>509853588</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SMP-RM-0003</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1409</v>
+        <v>1261</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3779,22 +3779,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>INV-0027</t>
+          <t>INV-0025</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>454387643</t>
+          <t>452916496</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -3806,11 +3806,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>505326615</t>
+          <t>508681625</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3818,15 +3818,15 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46285</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SMP-RM-0003</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>188</v>
+        <v>1891</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3835,22 +3835,22 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>INV-0024</t>
+          <t>INV-0039</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>457666510</t>
+          <t>452421902</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -3862,27 +3862,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>505633880</t>
+          <t>506254384</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SMP-RM-0001</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1620</v>
+        <v>249</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3891,22 +3891,22 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>INV-0044</t>
+          <t>INV-0011</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>459767135</t>
+          <t>457263036</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>502887752</t>
+          <t>509570219</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -3926,19 +3926,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SMP-RM-0005</t>
+          <t>SMP-RM-0020</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1170</v>
+        <v>292</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3947,22 +3947,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>INV-0037</t>
+          <t>INV-0036</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>452681144</t>
+          <t>457437584</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -3974,11 +3974,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>502694338</t>
+          <t>509164971</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3986,15 +3986,15 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>46282</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0006</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1807</v>
+        <v>1146</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4003,22 +4003,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>INV-0026</t>
+          <t>INV-0010</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>455431477</t>
+          <t>459214830</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -4030,27 +4030,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>508936405</t>
+          <t>504138993</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0020</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>835</v>
+        <v>119</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4059,22 +4059,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>INV-0009</t>
+          <t>INV-0055</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>457739741</t>
+          <t>457023677</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>506561547</t>
+          <t>503290672</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -4094,19 +4094,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SMP-RM-0016</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1895</v>
+        <v>1045</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>INV-0017</t>
+          <t>INV-0041</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>457248518</t>
+          <t>459304216</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4142,11 +4142,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>506084418</t>
+          <t>507973121</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4154,15 +4154,15 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>46311</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SMP-RM-0016</t>
+          <t>SMP-RM-0006</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1767</v>
+        <v>179</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4171,22 +4171,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>INV-0044</t>
+          <t>INV-0036</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>452647814</t>
+          <t>451517756</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -4198,27 +4198,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>503254614</t>
+          <t>505900455</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1595</v>
+        <v>1111</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4227,12 +4227,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>INV-0052</t>
+          <t>INV-0018</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>456383277</t>
+          <t>453822078</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4254,27 +4254,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>502497984</t>
+          <t>509309978</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>46303</v>
+        <v>46287</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SMP-RM-0007</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1880</v>
+        <v>1182</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>INV-0052</t>
+          <t>INV-0007</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>457831185</t>
+          <t>455494430</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4310,11 +4310,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>509665455</t>
+          <t>507154919</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4322,15 +4322,15 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1630</v>
+        <v>1128</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4339,22 +4339,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INV-0010</t>
+          <t>INV-0013</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>452100870</t>
+          <t>458132912</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -4366,27 +4366,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>507767679</t>
+          <t>505994727</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>69</v>
+        <v>723</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4395,22 +4395,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>INV-0011</t>
+          <t>INV-0055</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>454234033</t>
+          <t>452459332</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>501966829</t>
+          <t>504975295</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4430,19 +4430,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0019</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>113</v>
+        <v>1421</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4451,22 +4451,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INV-0058</t>
+          <t>INV-0022</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>457046090</t>
+          <t>458183451</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -4478,27 +4478,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>505596579</t>
+          <t>503335975</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>46289</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>822</v>
+        <v>1177</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4507,22 +4507,22 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>INV-0040</t>
+          <t>INV-0022</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>453078241</t>
+          <t>459930189</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>505059047</t>
+          <t>503824903</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4542,19 +4542,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>46290</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SMP-RM-0020</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>923</v>
+        <v>602</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4563,22 +4563,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>INV-0011</t>
+          <t>INV-0036</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>458962169</t>
+          <t>455485272</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -4590,27 +4590,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>506867997</t>
+          <t>502597613</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>46293</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1543</v>
+        <v>577</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>INV-0053</t>
+          <t>INV-0055</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>452516524</t>
+          <t>453128830</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4646,27 +4646,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>507485495</t>
+          <t>505188889</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1607</v>
+        <v>1706</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4675,22 +4675,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>INV-0013</t>
+          <t>INV-0015</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>454713654</t>
+          <t>457588425</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -4702,27 +4702,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>504468370</t>
+          <t>505508325</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1061</v>
+        <v>164</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>INV-0001</t>
+          <t>INV-0040</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>451149283</t>
+          <t>452561871</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4758,27 +4758,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>503905824</t>
+          <t>505667852</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1255</v>
+        <v>680</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4787,22 +4787,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>INV-0051</t>
+          <t>INV-0037</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>456124763</t>
+          <t>451041491</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -4814,27 +4814,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>508110298</t>
+          <t>508691502</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>46289</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>526</v>
+        <v>824</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>458829893</t>
+          <t>458208215</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -4870,27 +4870,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>507663113</t>
+          <t>509299939</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>46302</v>
+        <v>46285</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1366</v>
+        <v>701</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4899,22 +4899,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>INV-0053</t>
+          <t>INV-0035</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>457278533</t>
+          <t>453191007</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -4926,19 +4926,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>505742531</t>
+          <t>506766993</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>996</v>
+        <v>1292</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4955,22 +4955,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>INV-0004</t>
+          <t>INV-0050</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>456641903</t>
+          <t>458710502</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -4982,27 +4982,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>505645358</t>
+          <t>503650523</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SMP-RM-0010</t>
+          <t>SMP-RM-0001</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>395</v>
+        <v>1972</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5011,22 +5011,22 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>INV-0009</t>
+          <t>INV-0027</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>459678746</t>
+          <t>454394336</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -5038,27 +5038,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>501952520</t>
+          <t>506064462</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1404</v>
+        <v>1350</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>INV-0008</t>
+          <t>INV-0023</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>451427068</t>
+          <t>455200835</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>505959422</t>
+          <t>503777050</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5106,15 +5106,15 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>46291</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SMP-RM-0013</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>805</v>
+        <v>1496</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5123,22 +5123,22 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>INV-0047</t>
+          <t>INV-0044</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>451592554</t>
+          <t>454928281</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -5150,27 +5150,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>504186247</t>
+          <t>502596917</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1415</v>
+        <v>169</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5179,22 +5179,22 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INV-0034</t>
+          <t>INV-0008</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>458981512</t>
+          <t>454794852</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -5206,27 +5206,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>509511330</t>
+          <t>501155809</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>46282</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SMP-RM-0018</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>380</v>
+        <v>1683</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5235,22 +5235,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>INV-0018</t>
+          <t>INV-0007</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>452637507</t>
+          <t>458085252</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -5262,11 +5262,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>505339457</t>
+          <t>509014480</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5274,15 +5274,15 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46296</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1350</v>
+        <v>192</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5291,12 +5291,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>INV-0005</t>
+          <t>INV-0046</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>454728795</t>
+          <t>452718442</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5318,27 +5318,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>506152035</t>
+          <t>507166661</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>543</v>
+        <v>1594</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5347,22 +5347,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>INV-0037</t>
+          <t>INV-0052</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>455933359</t>
+          <t>453233823</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -5374,11 +5374,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>508894293</t>
+          <t>502147756</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5386,15 +5386,15 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0001</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1198</v>
+        <v>1259</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5403,22 +5403,22 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>INV-0039</t>
+          <t>INV-0041</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>452194801</t>
+          <t>453753418</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -5430,27 +5430,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>509396617</t>
+          <t>504574477</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SMP-RM-0013</t>
+          <t>SMP-RM-0020</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1095</v>
+        <v>1416</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5459,22 +5459,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>INV-0019</t>
+          <t>INV-0028</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>457930789</t>
+          <t>454644760</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -5486,27 +5486,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>503304606</t>
+          <t>503349030</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1176</v>
+        <v>729</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5515,22 +5515,22 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>INV-0057</t>
+          <t>INV-0027</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>458676774</t>
+          <t>456276495</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -5542,27 +5542,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>504025884</t>
+          <t>505157165</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>46307</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1302</v>
+        <v>518</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5571,22 +5571,22 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>INV-0011</t>
+          <t>INV-0035</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>456258215</t>
+          <t>455780177</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -5598,27 +5598,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>501079079</t>
+          <t>506060836</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>46291</v>
+        <v>46287</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SMP-RM-0007</t>
+          <t>SMP-RM-0020</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1568</v>
+        <v>1053</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>INV-0049</t>
+          <t>INV-0012</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>453828735</t>
+          <t>457572491</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5654,27 +5654,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>509213740</t>
+          <t>505015476</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>46293</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SMP-RM-0020</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>898</v>
+        <v>503</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -5683,22 +5683,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>INV-0040</t>
+          <t>INV-0031</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>458204299</t>
+          <t>452191383</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -5710,11 +5710,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>509009447</t>
+          <t>507058222</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5722,15 +5722,15 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>46299</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1103</v>
+        <v>1772</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -5739,22 +5739,22 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>INV-0012</t>
+          <t>INV-0053</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>457259602</t>
+          <t>458060918</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -5766,11 +5766,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>509909268</t>
+          <t>503898604</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>46311</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1293</v>
+        <v>1212</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5795,22 +5795,22 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>INV-0046</t>
+          <t>INV-0004</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>455174559</t>
+          <t>451231415</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -5822,27 +5822,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>506236039</t>
+          <t>501668183</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SMP-RM-0013</t>
+          <t>SMP-RM-0017</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1040</v>
+        <v>596</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5851,22 +5851,22 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>INV-0037</t>
+          <t>INV-0040</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>456135759</t>
+          <t>459406206</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -5878,27 +5878,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>501767026</t>
+          <t>508106413</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>46306</v>
+        <v>46287</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1500</v>
+        <v>1111</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5907,22 +5907,22 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>INV-0033</t>
+          <t>INV-0039</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>459793234</t>
+          <t>453561552</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -5934,27 +5934,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>503244614</t>
+          <t>506199374</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0007</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1546</v>
+        <v>1664</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -5963,22 +5963,22 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>INV-0012</t>
+          <t>INV-0009</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>453766286</t>
+          <t>459999133</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -5990,27 +5990,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>501320859</t>
+          <t>502109227</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>46282</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SMP-RM-0005</t>
+          <t>SMP-RM-0014</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>442</v>
+        <v>1504</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>INV-0046</t>
+          <t>INV-0054</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>451367643</t>
+          <t>455003671</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>503835093</t>
+          <t>502446410</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46293</v>
+        <v>46310</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>778</v>
+        <v>1263</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6075,22 +6075,22 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>INV-0056</t>
+          <t>INV-0038</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>455291430</t>
+          <t>451923227</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>501815153</t>
+          <t>503003921</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6114,15 +6114,15 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>46287</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SMP-RM-0004</t>
+          <t>SMP-RM-0005</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1348</v>
+        <v>1446</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6131,22 +6131,22 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>INV-0053</t>
+          <t>INV-0000</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>451331211</t>
+          <t>453748655</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -6158,27 +6158,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>507992333</t>
+          <t>509774573</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>46310</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SMP-RM-0004</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1130</v>
+        <v>351</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6187,22 +6187,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>INV-0016</t>
+          <t>INV-0023</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>458959049</t>
+          <t>453129542</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>504447632</t>
+          <t>502980663</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1365</v>
+        <v>567</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6243,22 +6243,22 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>INV-0006</t>
+          <t>INV-0033</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>459729340</t>
+          <t>452071594</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -6270,15 +6270,15 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>503301222</t>
+          <t>502293020</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1482</v>
+        <v>747</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>INV-0039</t>
+          <t>INV-0003</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>452975258</t>
+          <t>459382064</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6326,11 +6326,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>502782809</t>
+          <t>503799805</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6338,15 +6338,15 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>46302</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SMP-RM-0020</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>419</v>
+        <v>1593</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -6355,22 +6355,22 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>INV-0049</t>
+          <t>INV-0006</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>455412305</t>
+          <t>452934976</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -6382,27 +6382,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>504383514</t>
+          <t>501043092</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>46285</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>614</v>
+        <v>104</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -6411,12 +6411,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>INV-0010</t>
+          <t>INV-0030</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>451661118</t>
+          <t>457106512</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6438,27 +6438,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>504484526</t>
+          <t>504002466</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0014</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>15</v>
+        <v>469</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -6467,22 +6467,22 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>INV-0000</t>
+          <t>INV-0020</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>452493219</t>
+          <t>455165165</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -6494,27 +6494,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>509289690</t>
+          <t>505550953</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>46282</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0012</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -6523,22 +6523,22 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>INV-0046</t>
+          <t>INV-0032</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>452699372</t>
+          <t>451883692</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -6550,11 +6550,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>504878226</t>
+          <t>509653253</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6562,15 +6562,15 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>46283</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SMP-RM-0009</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>960</v>
+        <v>1806</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -6579,22 +6579,22 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>INV-0003</t>
+          <t>INV-0029</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>452674515</t>
+          <t>455736323</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -6606,27 +6606,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>501661769</t>
+          <t>506491198</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>882</v>
+        <v>26</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -6635,22 +6635,22 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>INV-0047</t>
+          <t>INV-0023</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>452944497</t>
+          <t>454366703</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -6662,27 +6662,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>501162274</t>
+          <t>506098752</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>46308</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0012</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>683</v>
+        <v>1221</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -6691,22 +6691,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>INV-0022</t>
+          <t>INV-0031</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>458343630</t>
+          <t>454278644</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -6718,27 +6718,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>502559464</t>
+          <t>505112546</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>46292</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0014</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>243</v>
+        <v>58</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -6747,22 +6747,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>INV-0025</t>
+          <t>INV-0014</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>457715084</t>
+          <t>456812025</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -6774,27 +6774,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>507471232</t>
+          <t>506620658</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>46297</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>241</v>
+        <v>1748</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -6803,22 +6803,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>INV-0008</t>
+          <t>INV-0047</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>451983923</t>
+          <t>456159172</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -6830,19 +6830,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>502740017</t>
+          <t>509888812</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>46284</v>
+        <v>46308</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1653</v>
+        <v>1978</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>INV-0036</t>
+          <t>INV-0003</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>458351152</t>
+          <t>453388630</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6886,27 +6886,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>507371160</t>
+          <t>502560728</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>46306</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SMP-RM-0001</t>
+          <t>SMP-RM-0017</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1776</v>
+        <v>855</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -6915,22 +6915,22 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>INV-0043</t>
+          <t>INV-0044</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>453192032</t>
+          <t>457249378</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -6942,27 +6942,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>502894776</t>
+          <t>502603516</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0013</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -6971,22 +6971,22 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>INV-0016</t>
+          <t>INV-0037</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>456272037</t>
+          <t>452044933</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -6998,27 +6998,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>504757843</t>
+          <t>504972370</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>46311</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1419</v>
+        <v>1906</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7027,22 +7027,22 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>INV-0044</t>
+          <t>INV-0051</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>452597897</t>
+          <t>457592651</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -7054,27 +7054,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>509085438</t>
+          <t>506336123</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SMP-RM-0013</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>INV-0053</t>
+          <t>INV-0012</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>451915467</t>
+          <t>453283577</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -7110,19 +7110,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>509482016</t>
+          <t>502828260</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>46311</v>
+        <v>46287</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>163</v>
+        <v>930</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>INV-0048</t>
+          <t>INV-0029</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>459248484</t>
+          <t>456268604</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -7166,11 +7166,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>506551494</t>
+          <t>509991321</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7178,15 +7178,15 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0015</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>466</v>
+        <v>641</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7195,22 +7195,22 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>INV-0035</t>
+          <t>INV-0029</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>457352484</t>
+          <t>455446095</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -7222,27 +7222,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>502322557</t>
+          <t>502517010</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>46299</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>927</v>
+        <v>1702</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -7251,22 +7251,22 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>INV-0005</t>
+          <t>INV-0045</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>459362706</t>
+          <t>451676621</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -7278,11 +7278,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>502991570</t>
+          <t>503488460</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7290,15 +7290,15 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>46297</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SMP-RM-0001</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>220</v>
+        <v>1993</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -7307,12 +7307,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>INV-0025</t>
+          <t>INV-0022</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>457917892</t>
+          <t>457647878</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7334,27 +7334,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>501002847</t>
+          <t>506013715</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>46310</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SMP-RM-0020</t>
+          <t>SMP-RM-0001</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1315</v>
+        <v>1959</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -7363,22 +7363,22 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>INV-0019</t>
+          <t>INV-0025</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>459528492</t>
+          <t>458586676</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -7390,11 +7390,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>508653898</t>
+          <t>505191831</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1682</v>
+        <v>1656</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -7419,22 +7419,22 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>INV-0014</t>
+          <t>INV-0050</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>458624573</t>
+          <t>453345338</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>508937865</t>
+          <t>502034637</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0007</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>243</v>
+        <v>1696</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -7475,22 +7475,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>INV-0006</t>
+          <t>INV-0025</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>454720299</t>
+          <t>457245146</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -7502,27 +7502,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>506958243</t>
+          <t>505342289</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>46311</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0003</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>775</v>
+        <v>414</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -7531,22 +7531,22 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>INV-0044</t>
+          <t>INV-0057</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>452783791</t>
+          <t>458439543</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -7558,27 +7558,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>509261472</t>
+          <t>502543145</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>46310</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>229</v>
+        <v>1939</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -7587,12 +7587,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>INV-0016</t>
+          <t>INV-0029</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>454287016</t>
+          <t>451849559</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7614,11 +7614,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>507591709</t>
+          <t>508267158</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7626,15 +7626,15 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SMP-RM-0007</t>
+          <t>SMP-RM-0001</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1477</v>
+        <v>793</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -7643,22 +7643,22 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>INV-0021</t>
+          <t>INV-0043</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>452808009</t>
+          <t>458158234</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -7670,11 +7670,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>501780146</t>
+          <t>504602338</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7682,15 +7682,15 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>46287</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SMP-RM-0015</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1358</v>
+        <v>923</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -7699,22 +7699,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>INV-0037</t>
+          <t>INV-0056</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>459459031</t>
+          <t>453493621</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -7726,27 +7726,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>501072773</t>
+          <t>505123584</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0014</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1143</v>
+        <v>1817</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -7755,22 +7755,22 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>INV-0059</t>
+          <t>INV-0035</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>458261353</t>
+          <t>459036805</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -7782,11 +7782,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>509102253</t>
+          <t>505693862</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -7794,15 +7794,15 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>46285</v>
+        <v>46310</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0014</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -7811,22 +7811,22 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>INV-0046</t>
+          <t>INV-0041</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>453153888</t>
+          <t>459821696</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -7838,27 +7838,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>506399642</t>
+          <t>501327658</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SMP-RM-0014</t>
+          <t>SMP-RM-0012</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1257</v>
+        <v>992</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -7867,22 +7867,22 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>INV-0058</t>
+          <t>INV-0034</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>455164755</t>
+          <t>459131572</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -7894,11 +7894,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>506752216</t>
+          <t>509428760</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -7906,15 +7906,15 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SMP-RM-0005</t>
+          <t>SMP-RM-0009</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>292</v>
+        <v>378</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>INV-0026</t>
+          <t>INV-0001</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>459594877</t>
+          <t>456349877</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -7950,27 +7950,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>506266549</t>
+          <t>501491630</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>46302</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SMP-RM-0007</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>421</v>
+        <v>1094</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -7979,22 +7979,22 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>INV-0013</t>
+          <t>INV-0022</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>455875114</t>
+          <t>454905100</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -8006,19 +8006,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>503225862</t>
+          <t>505158351</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>46290</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1431</v>
+        <v>1681</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8035,22 +8035,22 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>INV-0040</t>
+          <t>INV-0050</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>456408662</t>
+          <t>451937991</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -8062,27 +8062,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>506909569</t>
+          <t>507516648</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SMP-RM-0019</t>
+          <t>SMP-RM-0006</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1178</v>
+        <v>494</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>INV-0042</t>
+          <t>INV-0037</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>458004117</t>
+          <t>456335227</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -8118,27 +8118,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>505797075</t>
+          <t>501473227</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0019</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>228</v>
+        <v>301</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -8147,22 +8147,22 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>INV-0001</t>
+          <t>INV-0036</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>457389943</t>
+          <t>454158036</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -8174,11 +8174,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>501949670</t>
+          <t>506185050</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8186,15 +8186,15 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>46307</v>
+        <v>46285</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SMP-RM-0006</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>596</v>
+        <v>194</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -8203,22 +8203,22 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>INV-0043</t>
+          <t>INV-0003</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>455203716</t>
+          <t>454902772</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -8230,27 +8230,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>505951637</t>
+          <t>501334336</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>46307</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SMP-RM-0002</t>
+          <t>SMP-RM-0001</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>744</v>
+        <v>689</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -8259,22 +8259,22 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>INV-0052</t>
+          <t>INV-0058</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>458593275</t>
+          <t>454380011</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -8286,11 +8286,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>504763253</t>
+          <t>506716988</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8298,15 +8298,15 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>46308</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SMP-RM-0008</t>
+          <t>SMP-RM-0002</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1056</v>
+        <v>54</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>INV-0050</t>
+          <t>INV-0009</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>455825775</t>
+          <t>453376537</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -8342,27 +8342,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>507401894</t>
+          <t>509829762</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0012</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1988</v>
+        <v>1452</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -8371,12 +8371,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>INV-0035</t>
+          <t>INV-0042</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>451902651</t>
+          <t>457636992</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8398,27 +8398,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>504407238</t>
+          <t>506646557</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>46311</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SMP-RM-0012</t>
+          <t>SMP-RM-0005</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1556</v>
+        <v>332</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -8427,22 +8427,22 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>INV-0037</t>
+          <t>INV-0046</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>454296204</t>
+          <t>458329435</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP001</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Sample Steel Co.</t>
         </is>
       </c>
     </row>
@@ -8454,27 +8454,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>505935483</t>
+          <t>506323132</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SMP-RM-0003</t>
+          <t>SMP-RM-0018</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>392</v>
+        <v>1430</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -8483,22 +8483,22 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>INV-0011</t>
+          <t>INV-0056</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>459620919</t>
+          <t>456986539</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>501681729</t>
+          <t>503941912</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -8522,15 +8522,15 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SMP-RM-0018</t>
+          <t>SMP-RM-0010</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>551</v>
+        <v>270</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -8539,22 +8539,22 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>INV-0008</t>
+          <t>INV-0011</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>453699938</t>
+          <t>451030163</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>SUP004</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Fictional Metals</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -8566,27 +8566,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>501094709</t>
+          <t>507569981</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>RM02</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SMP-RM-0005</t>
+          <t>SMP-RM-0020</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>91</v>
+        <v>661</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -8595,22 +8595,22 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>INV-0009</t>
+          <t>INV-0058</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>456412833</t>
+          <t>454706007</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>506052539</t>
+          <t>502746679</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -8630,19 +8630,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM01</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SMP-RM-0018</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>743</v>
+        <v>1536</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -8656,17 +8656,17 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>456332789</t>
+          <t>454992909</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>SUP001</t>
+          <t>SUP005</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Sample Steel Co.</t>
+          <t>Test Logistics Parts</t>
         </is>
       </c>
     </row>
@@ -8678,27 +8678,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>504084811</t>
+          <t>503816683</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>RM01</t>
+          <t>COIL</t>
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SMP-RM-0017</t>
+          <t>SMP-RM-0011</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>336</v>
+        <v>924</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -8707,22 +8707,22 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>INV-0026</t>
+          <t>INV-0000</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>457768215</t>
+          <t>455449526</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP003</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Example Coatings</t>
         </is>
       </c>
     </row>
@@ -8734,27 +8734,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>504711087</t>
+          <t>502137407</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>46309</v>
+        <v>46305</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0004</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>688</v>
+        <v>1485</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -8763,22 +8763,22 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>INV-0023</t>
+          <t>INV-0000</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>455925360</t>
+          <t>451807780</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>SUP003</t>
+          <t>SUP002</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Example Coatings</t>
+          <t>Demo Fasteners Inc.</t>
         </is>
       </c>
     </row>
@@ -8790,27 +8790,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>509900294</t>
+          <t>508040612</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>COIL</t>
+          <t>RM02</t>
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SMP-RM-0001</t>
+          <t>SMP-RM-0016</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>244</v>
+        <v>1815</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -8819,22 +8819,22 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>INV-0042</t>
+          <t>INV-0024</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>456805039</t>
+          <t>456892681</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>SUP005</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Test Logistics Parts</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
@@ -8846,11 +8846,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>505090740</t>
+          <t>502701688</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -8858,15 +8858,15 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SMP-RM-0011</t>
+          <t>SMP-RM-0008</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>791</v>
+        <v>343</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -8875,22 +8875,22 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>INV-0058</t>
+          <t>INV-0028</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>452902100</t>
+          <t>452236638</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>SUP002</t>
+          <t>SUP004</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Demo Fasteners Inc.</t>
+          <t>Fictional Metals</t>
         </is>
       </c>
     </row>
